--- a/rmonize/data_dictionary/DD_LISA_P2.xlsx
+++ b/rmonize/data_dictionary/DD_LISA_P2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5690281B-013C-4C48-9F4A-DB505DF55E78}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8CB1C8-81AB-4699-BB43-465BC78BC798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22050" windowHeight="8280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11025" yWindow="0" windowWidth="11025" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="192">
   <si>
     <t>index</t>
   </si>
@@ -605,6 +605,12 @@
   </si>
   <si>
     <t>LDL cholesterol [mmol/L]</t>
+  </si>
+  <si>
+    <t>General or specialist university entrance qualification</t>
+  </si>
+  <si>
+    <t>Other degree</t>
   </si>
 </sst>
 </file>
@@ -772,9 +778,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -812,7 +818,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -918,7 +924,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1060,7 +1066,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2542,7 +2548,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2553,7 +2559,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2970,15 +2976,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B1DC67C611DD5E4D81775F9F3E26A7B2" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7f379a5812b480a74f9d031be5f88a83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xmlns:ns3="12535b08-222e-45d2-b6db-15019f1afee6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbce1e37d7de67e1c835013ca0ee7a7c" ns2:_="" ns3:_="">
     <xsd:import namespace="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
@@ -3219,6 +3216,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9CBEFE-8C4C-4054-8E02-CA457E93B4C8}">
   <ds:schemaRefs>
@@ -3231,14 +3237,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A35BFFB-6462-4C07-9656-4D34A1531B24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3255,4 +3253,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/rmonize/data_dictionary/DD_LISA_P2.xlsx
+++ b/rmonize/data_dictionary/DD_LISA_P2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8CB1C8-81AB-4699-BB43-465BC78BC798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C2B37C-38D6-457B-BB5E-E9FC15D614A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11025" yWindow="0" windowWidth="11025" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="202">
   <si>
     <t>index</t>
   </si>
@@ -469,27 +469,6 @@
     <t>female</t>
   </si>
   <si>
-    <t>No secondary school or elementary school certificate</t>
-  </si>
-  <si>
-    <t>Lower secondary school or elementary school certificate</t>
-  </si>
-  <si>
-    <t>Secondary school certificate (middle school leaving certificate)</t>
-  </si>
-  <si>
-    <t>Completion of Polytechnic. high school</t>
-  </si>
-  <si>
-    <t>Advanced technical college entrance qualification</t>
-  </si>
-  <si>
-    <t>general or specialist university entrance qualification</t>
-  </si>
-  <si>
-    <t>other degree</t>
-  </si>
-  <si>
     <t>fully employed (100%)</t>
   </si>
   <si>
@@ -607,10 +586,61 @@
     <t>LDL cholesterol [mmol/L]</t>
   </si>
   <si>
-    <t>General or specialist university entrance qualification</t>
-  </si>
-  <si>
-    <t>Other degree</t>
+    <t>kein Haupt- oder Volksschulabschluss</t>
+  </si>
+  <si>
+    <t>Haupt- oder Volksschulabschluss</t>
+  </si>
+  <si>
+    <t>Realschulabschluss (mittlere Reife)</t>
+  </si>
+  <si>
+    <t>Abschluss der Polytechn. Oberschule</t>
+  </si>
+  <si>
+    <t>Fachhochschulreife</t>
+  </si>
+  <si>
+    <t>allgem. oder fachgeb. Hochschulreife</t>
+  </si>
+  <si>
+    <t>anderer Abschluss</t>
+  </si>
+  <si>
+    <t>MUTBERU_0</t>
+  </si>
+  <si>
+    <t>Auszubildende/r, Student/in</t>
+  </si>
+  <si>
+    <t>kein beruflicher Abschluss</t>
+  </si>
+  <si>
+    <t>abgeschlossene beruflich-betriebliche Ausbildung</t>
+  </si>
+  <si>
+    <t>abgeschlossene beruflich-schulische Ausbildung</t>
+  </si>
+  <si>
+    <t>abgeschlossene Ausbildung an Fachschule</t>
+  </si>
+  <si>
+    <t>Fachhochschulabschluss</t>
+  </si>
+  <si>
+    <t>Hochschulabschluss</t>
+  </si>
+  <si>
+    <t>anderer beruflicher Abschluss</t>
+  </si>
+  <si>
+    <t>VATBERU_0</t>
+  </si>
+  <si>
+    <t>highest job qualification of the mother</t>
+  </si>
+  <si>
+    <t>highest job qualification of the father</t>
   </si>
 </sst>
 </file>
@@ -695,7 +725,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -738,17 +768,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -760,9 +781,21 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -778,9 +811,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -818,7 +851,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -924,7 +957,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1066,7 +1099,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1074,8 +1107,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I141"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I143"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="9"/>
     <col min="2" max="2" width="18.85546875" style="12" bestFit="1" customWidth="1"/>
@@ -1084,16 +1117,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1102,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
@@ -1168,17 +1201,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="B7" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1186,53 +1219,53 @@
       <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="B8" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>20</v>
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>21</v>
+      <c r="B10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>171</v>
+      <c r="B11" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>5</v>
@@ -1242,100 +1275,98 @@
       <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>174</v>
+      <c r="B12" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>175</v>
+      <c r="B13" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>172</v>
+      <c r="B14" s="17" t="s">
+        <v>167</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>173</v>
+      <c r="B15" s="17" t="s">
+        <v>168</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>28</v>
+      <c r="B16" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>29</v>
+      <c r="B17" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>31</v>
+      <c r="B18" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" s="9"/>
     </row>
@@ -1343,468 +1374,470 @@
       <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>34</v>
+      <c r="B19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>10</v>
       </c>
+      <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>38</v>
+      <c r="B22" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>39</v>
+      <c r="B23" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>44</v>
+      <c r="B25" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>46</v>
+      <c r="B26" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>26</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>48</v>
+      <c r="B27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>50</v>
+      <c r="B28" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>28</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>29</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>184</v>
+      <c r="B30" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="B31" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>55</v>
+      <c r="B31" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="F31" s="9"/>
+    </row>
+    <row r="32" spans="1:6" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>59</v>
+      <c r="B33" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D40" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="D41" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>188</v>
+        <v>75</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>185</v>
+        <v>76</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>80</v>
+      <c r="B46" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>83</v>
+      <c r="B47" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>47</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>85</v>
+        <v>80</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="D48" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>48</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>10</v>
       </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>49</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>10</v>
       </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>50</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>10</v>
@@ -1815,10 +1848,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>10</v>
@@ -1829,10 +1862,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>10</v>
@@ -1843,10 +1876,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>10</v>
@@ -1857,10 +1890,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>10</v>
@@ -1871,25 +1904,24 @@
         <v>55</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D56" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>56</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>10</v>
@@ -1900,58 +1932,53 @@
         <v>57</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D58" s="12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>58</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>59</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>60</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>10</v>
@@ -1965,10 +1992,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>10</v>
@@ -1981,11 +2008,11 @@
       <c r="A63" s="9">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>114</v>
+      <c r="B63" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>10</v>
@@ -1998,11 +2025,11 @@
       <c r="A64" s="9">
         <v>63</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>116</v>
+      <c r="B64" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>10</v>
@@ -2016,16 +2043,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D65" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G65" s="4"/>
-      <c r="H65" s="14"/>
+      <c r="H65" s="3"/>
       <c r="I65" s="3"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2033,10 +2060,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>10</v>
@@ -2050,16 +2077,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="4"/>
-      <c r="H67" s="3"/>
+      <c r="H67" s="14"/>
       <c r="I67" s="3"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2067,10 +2094,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>10</v>
@@ -2084,16 +2111,15 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="G69" s="4"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
     </row>
@@ -2102,15 +2128,15 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G70" s="3"/>
+      <c r="G70" s="4"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
@@ -2118,28 +2144,29 @@
       <c r="A71" s="9">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="s">
-        <v>130</v>
+      <c r="B71" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D71" s="12" t="s">
         <v>10</v>
       </c>
+      <c r="E71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
-    <row r="72" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>71</v>
       </c>
-      <c r="B72" s="12" t="s">
-        <v>132</v>
+      <c r="B72" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D72" s="12" t="s">
         <v>10</v>
@@ -2153,10 +2180,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>10</v>
@@ -2165,15 +2192,15 @@
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>73</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>10</v>
@@ -2187,24 +2214,27 @@
         <v>74</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D75" s="12" t="s">
         <v>10</v>
       </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>75</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="D76" s="12" t="s">
         <v>10</v>
@@ -2218,10 +2248,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="D77" s="12" t="s">
         <v>10</v>
@@ -2232,27 +2262,48 @@
         <v>77</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-    </row>
-    <row r="82" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="9">
+        <v>78</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="9">
+        <v>79</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="83" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G83" s="4"/>
+      <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
@@ -2262,7 +2313,7 @@
       <c r="I84" s="3"/>
     </row>
     <row r="85" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G85" s="3"/>
+      <c r="G85" s="4"/>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
     </row>
@@ -2343,50 +2394,54 @@
     </row>
     <row r="101" spans="7:9" x14ac:dyDescent="0.25">
       <c r="G101" s="3"/>
-    </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B114" s="9"/>
-    </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+    </row>
+    <row r="102" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+    </row>
+    <row r="103" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G103" s="3"/>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B116" s="9"/>
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G119" s="14"/>
+      <c r="G119" s="3"/>
       <c r="H119" s="3"/>
       <c r="I119" s="3"/>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G120" s="14"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-    </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G121" s="4"/>
+      <c r="G121" s="14"/>
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G122" s="3"/>
+      <c r="G122" s="14"/>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G123" s="3"/>
-      <c r="H123" s="6"/>
+      <c r="G123" s="4"/>
+      <c r="H123" s="3"/>
       <c r="I123" s="3"/>
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G124" s="4"/>
+      <c r="G124" s="3"/>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D125" s="9"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="3"/>
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D126" s="9"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D127" s="9"/>
@@ -2432,6 +2487,12 @@
     </row>
     <row r="141" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D141" s="9"/>
+    </row>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D142" s="9"/>
+    </row>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D143" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -2441,8 +2502,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.42578125" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" style="3" customWidth="1"/>
@@ -2455,7 +2516,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2467,7 +2528,7 @@
       <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="23">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2478,275 +2539,275 @@
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="23">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="21" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C4" s="21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="13">
         <v>2</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C5" s="21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="13">
         <v>3</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>146</v>
+      <c r="C6" s="21" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="13">
         <v>4</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C7" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C8" s="21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="13">
         <v>6</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>190</v>
+      <c r="C9" s="21" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="13">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C10" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="13">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C11" s="21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="13">
         <v>2</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C12" s="21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="13">
         <v>3</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>146</v>
+      <c r="C13" s="21" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="13">
         <v>4</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C14" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="13">
         <v>5</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C15" s="21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="13">
         <v>6</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>149</v>
+      <c r="C16" s="21" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="13">
         <v>7</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>150</v>
+      <c r="C17" s="21" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="13">
         <v>1</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>151</v>
+      <c r="C18" s="21" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="13">
         <v>2</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>152</v>
+      <c r="C19" s="21" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="13">
         <v>3</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>153</v>
+      <c r="C20" s="21" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="13">
         <v>4</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>154</v>
+      <c r="C21" s="21" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="13">
         <v>5</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>155</v>
+      <c r="C22" s="21" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B23" s="13">
         <v>1</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>151</v>
+      <c r="C23" s="21" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="13">
         <v>2</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>152</v>
+      <c r="C24" s="21" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="13">
         <v>3</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>153</v>
+      <c r="C25" s="21" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="13">
         <v>4</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>154</v>
+      <c r="C26" s="21" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="21" t="s">
         <v>17</v>
       </c>
       <c r="B27" s="13">
         <v>5</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>155</v>
+      <c r="C27" s="21" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2756,8 +2817,8 @@
       <c r="B28" s="13">
         <v>1</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>156</v>
+      <c r="C28" s="21" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2767,195 +2828,371 @@
       <c r="B29" s="13">
         <v>2</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>157</v>
+      <c r="C29" s="21" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="24">
         <v>1</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>158</v>
+      <c r="C30" s="21" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="24">
         <v>2</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>159</v>
+      <c r="C31" s="21" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="24">
         <v>3</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>160</v>
+      <c r="C32" s="21" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="24">
         <v>4</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>161</v>
+      <c r="C33" s="21" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="24">
         <v>5</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>162</v>
+      <c r="C34" s="21" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="24">
         <v>1</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>163</v>
+      <c r="C35" s="21" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="24">
         <v>2</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>164</v>
+      <c r="C36" s="21" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="17">
+        <v>158</v>
+      </c>
+      <c r="B37" s="24">
         <v>0</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>166</v>
+      <c r="C37" s="21" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B38" s="17">
+        <v>158</v>
+      </c>
+      <c r="B38" s="24">
         <v>1</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>167</v>
+      <c r="C38" s="21" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B39" s="17">
+        <v>158</v>
+      </c>
+      <c r="B39" s="24">
         <v>2</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>158</v>
+      <c r="C39" s="21" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B40" s="17">
+        <v>158</v>
+      </c>
+      <c r="B40" s="24">
         <v>3</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>168</v>
+      <c r="C40" s="21" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="24">
         <v>1</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>167</v>
+      <c r="C41" s="21" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="24">
         <v>2</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>158</v>
+      <c r="C42" s="21" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="24">
         <v>3</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>169</v>
+      <c r="C43" s="21" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="24">
         <v>1</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>167</v>
+      <c r="C44" s="21" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="24">
         <v>2</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>158</v>
+      <c r="C45" s="21" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="24">
         <v>3</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>169</v>
+      <c r="C46" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" s="24">
+        <v>1</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B48" s="24">
+        <v>2</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B49" s="24">
+        <v>3</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="24">
+        <v>4</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B51" s="24">
+        <v>5</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B52" s="24">
+        <v>6</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B53" s="24">
+        <v>7</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B54" s="24">
+        <v>8</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" s="24">
+        <v>1</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" s="24">
+        <v>2</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" s="24">
+        <v>3</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B58" s="24">
+        <v>4</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" s="24">
+        <v>5</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B60" s="24">
+        <v>6</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B61" s="24">
+        <v>7</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B62" s="24">
+        <v>8</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/rmonize/data_dictionary/DD_LISA_P2.xlsx
+++ b/rmonize/data_dictionary/DD_LISA_P2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C2B37C-38D6-457B-BB5E-E9FC15D614A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601EAEFE-EEC2-4E29-92A2-340237AAAA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11025" yWindow="0" windowWidth="11025" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -725,7 +728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -738,15 +741,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -811,9 +805,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -851,7 +845,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -957,7 +951,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1099,7 +1093,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1107,34 +1101,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="9"/>
-    <col min="2" max="2" width="18.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="12"/>
+    <col min="1" max="1" width="11.42578125" style="6"/>
+    <col min="2" max="2" width="18.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+    <row r="2" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>175</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -1144,219 +1138,218 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:4" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+    </row>
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="D4" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="18" t="s">
         <v>190</v>
       </c>
       <c r="C7" t="s">
         <v>200</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+    <row r="12" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+    <row r="13" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+    <row r="14" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+    <row r="15" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
+    <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+    <row r="17" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1365,1134 +1358,931 @@
       <c r="C18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+      <c r="D20" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+      <c r="D21" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
+      <c r="D22" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="6" t="s">
         <v>176</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
+      <c r="D23" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+    <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+      <c r="D25" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+    </row>
+    <row r="27" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+    <row r="28" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
+      <c r="D28" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
+      <c r="D29" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+      <c r="D30" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="1:6" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
+      <c r="D31" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+      <c r="D32" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
+      <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="9">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
+      <c r="A37" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
+      <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
+      <c r="A39" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="9">
+      <c r="A40" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="9">
+      <c r="A42" s="6">
         <v>41</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
+      <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="9">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
+      <c r="A45" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="6" t="s">
         <v>179</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="9">
+      <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="6" t="s">
         <v>178</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="9">
+      <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
+      <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="9">
+      <c r="D48" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="9">
+      <c r="D49" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="9">
+      <c r="D50" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D51" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="9">
+      <c r="D51" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="9">
+      <c r="D52" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D53" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="9">
+      <c r="D53" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="9">
+      <c r="D54" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="9">
+      <c r="D55" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="9">
+      <c r="D56" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="9">
+      <c r="D57" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D58" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="9">
+      <c r="D58" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D59" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="9">
+      <c r="D59" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D60" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="9">
+      <c r="D60" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D61" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="9">
+      <c r="D61" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D62" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="9">
+      <c r="D62" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="9">
+      <c r="D63" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D64" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="9">
+      <c r="D64" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D65" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="4"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="9">
+      <c r="D65" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D66" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="4"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="9">
+      <c r="D66" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="4"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="3"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="9">
+      <c r="D67" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D68" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="4"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="9">
+      <c r="D68" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D69" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="4"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="9">
+      <c r="D69" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D70" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70" s="4"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="9">
+      <c r="D70" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D71" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="9">
+      <c r="D71" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D72" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="9">
+      <c r="D72" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-    </row>
-    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="9">
+      <c r="D73" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
         <v>73</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="9">
+      <c r="D74" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D75" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="9">
+      <c r="D75" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
         <v>75</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D76" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="9">
+      <c r="D76" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
         <v>76</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="9">
+      <c r="D77" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
         <v>77</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D78" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="9">
+      <c r="D78" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D79" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="9">
+      <c r="D79" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D80" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-    </row>
-    <row r="84" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-    </row>
-    <row r="85" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G85" s="4"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-    </row>
-    <row r="86" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
-    </row>
-    <row r="87" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-    </row>
-    <row r="88" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-    </row>
-    <row r="89" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
-    </row>
-    <row r="90" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-    </row>
-    <row r="91" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-    </row>
-    <row r="92" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-    </row>
-    <row r="93" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-    </row>
-    <row r="94" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-    </row>
-    <row r="95" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-    </row>
-    <row r="96" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-    </row>
-    <row r="97" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-    </row>
-    <row r="98" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
-    </row>
-    <row r="99" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
-    </row>
-    <row r="100" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
-    </row>
-    <row r="101" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-    </row>
-    <row r="102" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-    </row>
-    <row r="103" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G103" s="3"/>
-    </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B116" s="9"/>
-    </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-    </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G121" s="14"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="3"/>
-    </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G122" s="14"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="3"/>
-    </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G123" s="4"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="3"/>
-    </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
-      <c r="I124" s="3"/>
-    </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G125" s="3"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="3"/>
-    </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G126" s="4"/>
-      <c r="H126" s="3"/>
-      <c r="I126" s="3"/>
-    </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D127" s="9"/>
-    </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D128" s="9"/>
+      <c r="D80" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" s="6"/>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D127" s="6"/>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D128" s="6"/>
     </row>
     <row r="129" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D129" s="9"/>
+      <c r="D129" s="6"/>
     </row>
     <row r="130" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D130" s="9"/>
+      <c r="D130" s="6"/>
     </row>
     <row r="131" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D131" s="9"/>
+      <c r="D131" s="6"/>
     </row>
     <row r="132" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D132" s="9"/>
+      <c r="D132" s="6"/>
     </row>
     <row r="133" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D133" s="9"/>
+      <c r="D133" s="6"/>
     </row>
     <row r="134" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D134" s="9"/>
+      <c r="D134" s="6"/>
     </row>
     <row r="135" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D135" s="9"/>
+      <c r="D135" s="6"/>
     </row>
     <row r="136" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D136" s="9"/>
+      <c r="D136" s="6"/>
     </row>
     <row r="137" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D137" s="9"/>
+      <c r="D137" s="6"/>
     </row>
     <row r="138" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D138" s="9"/>
+      <c r="D138" s="6"/>
     </row>
     <row r="139" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D139" s="9"/>
+      <c r="D139" s="6"/>
     </row>
     <row r="140" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D140" s="9"/>
+      <c r="D140" s="6"/>
     </row>
     <row r="141" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D141" s="9"/>
+      <c r="D141" s="6"/>
     </row>
     <row r="142" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D142" s="9"/>
+      <c r="D142" s="6"/>
     </row>
     <row r="143" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D143" s="9"/>
+      <c r="D143" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -2502,333 +2292,332 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.42578125" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="20">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="20">
         <v>2</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="10">
         <v>1</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="18" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="10">
         <v>2</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="18" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="10">
         <v>3</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="18" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="10">
         <v>4</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="18" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="10">
         <v>5</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="18" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="10">
         <v>6</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="18" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="10">
         <v>7</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="18" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="10">
         <v>1</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="18" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="10">
         <v>2</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="18" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="10">
         <v>3</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="18" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="10">
         <v>4</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="18" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="10">
         <v>5</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="18" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="10">
         <v>6</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="18" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="10">
         <v>7</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="10">
         <v>1</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="18" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="10">
         <v>2</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="18" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="10">
         <v>3</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="18" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="10">
         <v>4</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="18" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="10">
         <v>5</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="18" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="10">
         <v>1</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="18" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="10">
         <v>2</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="18" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="10">
         <v>3</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="18" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="10">
         <v>4</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="18" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="10">
         <v>5</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="18" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="10">
         <v>1</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="18" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="10">
         <v>2</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="18" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2836,10 +2625,10 @@
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="21">
         <v>1</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="18" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2847,10 +2636,10 @@
       <c r="A31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="21">
         <v>2</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="18" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2858,10 +2647,10 @@
       <c r="A32" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="21">
         <v>3</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="18" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2869,10 +2658,10 @@
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="21">
         <v>4</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="18" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2880,318 +2669,318 @@
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="21">
         <v>5</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="18" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="21">
         <v>1</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="18" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="21">
         <v>2</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="18" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="21">
         <v>0</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="18" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="21">
         <v>1</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="21">
         <v>2</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" s="18" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="21">
         <v>3</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="18" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="21">
         <v>1</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="21">
         <v>2</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="18" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B43" s="21">
         <v>3</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C43" s="18" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="21">
         <v>1</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B45" s="21">
         <v>2</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="18" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B46" s="21">
         <v>3</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="18" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B47" s="21">
         <v>1</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="18" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B48" s="21">
         <v>2</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="18" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="21">
         <v>3</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="C49" s="18" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B50" s="21">
         <v>4</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="18" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B51" s="21">
         <v>5</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="18" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="21">
         <v>6</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="18" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
+      <c r="A53" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B53" s="21">
         <v>7</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" s="18" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B54" s="21">
         <v>8</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="18" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B55" s="21">
         <v>1</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="18" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B56" s="21">
         <v>2</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="18" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B57" s="21">
         <v>3</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="18" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B58" s="24">
+      <c r="B58" s="21">
         <v>4</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="18" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B59" s="24">
+      <c r="B59" s="21">
         <v>5</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="18" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B60" s="24">
+      <c r="B60" s="21">
         <v>6</v>
       </c>
-      <c r="C60" s="21" t="s">
+      <c r="C60" s="18" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
+      <c r="A61" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B61" s="24">
+      <c r="B61" s="21">
         <v>7</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="18" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="21" t="s">
+      <c r="A62" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B62" s="24">
+      <c r="B62" s="21">
         <v>8</v>
       </c>
-      <c r="C62" s="21" t="s">
+      <c r="C62" s="18" t="s">
         <v>198</v>
       </c>
     </row>
@@ -3213,6 +3002,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B1DC67C611DD5E4D81775F9F3E26A7B2" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7f379a5812b480a74f9d031be5f88a83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b63cdcf7-47fa-43f6-87e5-23b415b5c413" xmlns:ns3="12535b08-222e-45d2-b6db-15019f1afee6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbce1e37d7de67e1c835013ca0ee7a7c" ns2:_="" ns3:_="">
     <xsd:import namespace="b63cdcf7-47fa-43f6-87e5-23b415b5c413"/>
@@ -3453,15 +3251,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9CBEFE-8C4C-4054-8E02-CA457E93B4C8}">
   <ds:schemaRefs>
@@ -3474,6 +3263,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A35BFFB-6462-4C07-9656-4D34A1531B24}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3490,12 +3287,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C05FF1B-7508-40EF-8319-E993EA07F007}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>